--- a/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED02.xlsx
+++ b/data/simulations/xa_fixed_v1/SIM_XA_FIXED_seed_20260809/competition_xlsx/企业数据/SIM_XA_FIXED02.xlsx
@@ -472,7 +472,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>2026-08-09T17:31:57+08:00</t>
+          <t>2026-08-09T17:48:52+08:00</t>
         </is>
       </c>
     </row>
@@ -484,7 +484,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>242W</t>
+          <t>183W</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -753,7 +753,7 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1617,7 +1617,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L5"/>
+  <dimension ref="B2:L4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="2" max="2"/>
@@ -1700,7 +1700,7 @@
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>SIM_XA_FIXED-2-0032</t>
+          <t>SIM_XA_FIXED-3-0114</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1714,11 +1714,11 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>147W</t>
+          <t>33W</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>第2年</t>
+          <t>第3年</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4季</t>
+          <t>2季</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1748,62 +1748,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>第3年3季</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SIM_XA_FIXED-4-0048</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>本地</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>P1</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>81W</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>已交</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>第4年</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>5季</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>2季</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>第5年1季</t>
+          <t>第3年4季</t>
         </is>
       </c>
     </row>
@@ -1821,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G52"/>
+  <dimension ref="B2:G50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="2" max="2"/>
@@ -2141,10 +2086,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="E14" t="n">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2153,7 +2098,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 0}</t>
         </is>
       </c>
     </row>
@@ -2170,7 +2115,7 @@
         <v>-14</v>
       </c>
       <c r="E15" t="n">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2196,7 +2141,7 @@
         <v>-14</v>
       </c>
       <c r="E16" t="n">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2222,7 +2167,7 @@
         <v>-14</v>
       </c>
       <c r="E17" t="n">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2248,7 +2193,7 @@
         <v>-14</v>
       </c>
       <c r="E18" t="n">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2274,7 +2219,7 @@
         <v>-15</v>
       </c>
       <c r="E19" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2300,7 +2245,7 @@
         <v>0</v>
       </c>
       <c r="E20" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2326,7 +2271,7 @@
         <v>0</v>
       </c>
       <c r="E21" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2345,14 +2290,14 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>-48</v>
+        <v>-8</v>
       </c>
       <c r="E22" t="n">
-        <v>361</v>
+        <v>405</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -2361,7 +2306,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2371,14 +2316,14 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>-32</v>
+        <v>-14</v>
       </c>
       <c r="E23" t="n">
-        <v>329</v>
+        <v>391</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -2387,7 +2332,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-f169011452", "line_id": "L-02a70490e9", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2397,23 +2342,23 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D24" t="n">
         <v>-12</v>
       </c>
       <c r="E24" t="n">
-        <v>317</v>
+        <v>379</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2423,23 +2368,23 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E25" t="n">
-        <v>303</v>
+        <v>371</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>第3年1季</t>
+          <t>第3年2季</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-264ae4b3f0", "line_id": "L-02a70490e9", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2456,7 +2401,7 @@
         <v>-14</v>
       </c>
       <c r="E26" t="n">
-        <v>289</v>
+        <v>357</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -2475,14 +2420,14 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>0</v>
+        <v>-14</v>
       </c>
       <c r="E27" t="n">
-        <v>289</v>
+        <v>343</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2491,7 +2436,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 80.0, "order_id": "SIM_XA_FIXED-2-0032", "receivable_term_quarters": 4, "revenue_wan": 147.0}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2501,23 +2446,23 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Emergency_Buy_Material</t>
+          <t>Sell_Product</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>-48</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
-        <v>241</v>
+        <v>343</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>emergency_material_purchase | {"cost_wan": 48.0, "material_id": "R1", "quantity": 4.0}</t>
+          <t>order_delivered | {"cost_of_goods_sold_wan": 20.0, "order_id": "SIM_XA_FIXED-3-0114", "receivable_term_quarters": 2, "revenue_wan": 33.0}</t>
         </is>
       </c>
     </row>
@@ -2527,23 +2472,23 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Product_Produce</t>
+          <t>Emergency_Buy_Material</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>-32</v>
+        <v>-12</v>
       </c>
       <c r="E29" t="n">
-        <v>209</v>
+        <v>331</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>production_started | {"job": {"inventory_cost_wan": 80.0, "job_id": "JOB-7ca2cf9232", "line_id": "L-02a70490e9", "product_id": "P1", "quantity": 4.0, "remaining_quarters": 0}}</t>
+          <t>emergency_material_purchase | {"cost_wan": 12.0, "material_id": "R1", "quantity": 1.0}</t>
         </is>
       </c>
     </row>
@@ -2553,23 +2498,23 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Product_Produce</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>-14</v>
+        <v>-8</v>
       </c>
       <c r="E30" t="n">
-        <v>195</v>
+        <v>323</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>第3年3季</t>
+          <t>第3年4季</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>production_started | {"job": {"inventory_cost_wan": 20.0, "job_id": "JOB-c2de99b0c8", "line_id": "L-02a70490e9", "product_id": "P1", "quantity": 1.0, "remaining_quarters": 0}}</t>
         </is>
       </c>
     </row>
@@ -2586,7 +2531,7 @@
         <v>-14</v>
       </c>
       <c r="E31" t="n">
-        <v>181</v>
+        <v>309</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -2612,7 +2557,7 @@
         <v>-15</v>
       </c>
       <c r="E32" t="n">
-        <v>166</v>
+        <v>294</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -2638,7 +2583,7 @@
         <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>166</v>
+        <v>294</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -2664,7 +2609,7 @@
         <v>0</v>
       </c>
       <c r="E34" t="n">
-        <v>166</v>
+        <v>294</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2687,10 +2632,10 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>-12</v>
+        <v>-8</v>
       </c>
       <c r="E35" t="n">
-        <v>154</v>
+        <v>286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2699,7 +2644,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 1}</t>
         </is>
       </c>
     </row>
@@ -2716,7 +2661,7 @@
         <v>-14</v>
       </c>
       <c r="E36" t="n">
-        <v>140</v>
+        <v>272</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2735,23 +2680,23 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Update_Receivable</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>-14</v>
+        <v>33</v>
       </c>
       <c r="E37" t="n">
-        <v>126</v>
+        <v>305</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>第4年2季</t>
+          <t>第4年1季</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>receivable_collected | {"receivable_id": "AR-f0f90d2128"}</t>
         </is>
       </c>
     </row>
@@ -2761,14 +2706,14 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>147</v>
+        <v>-14</v>
       </c>
       <c r="E38" t="n">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -2777,7 +2722,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-79aa24a817"}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2739,7 @@
         <v>-14</v>
       </c>
       <c r="E39" t="n">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -2820,7 +2765,7 @@
         <v>-14</v>
       </c>
       <c r="E40" t="n">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -2846,7 +2791,7 @@
         <v>-15</v>
       </c>
       <c r="E41" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -2872,7 +2817,7 @@
         <v>0</v>
       </c>
       <c r="E42" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -2898,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="E43" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -2917,14 +2862,14 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sell_Product</t>
+          <t>Pay_AD</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>0</v>
+        <v>-8</v>
       </c>
       <c r="E44" t="n">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -2933,7 +2878,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>order_delivered | {"cost_of_goods_sold_wan": 40.0, "order_id": "SIM_XA_FIXED-4-0048", "receivable_term_quarters": 2, "revenue_wan": 81.0}</t>
+          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
         </is>
       </c>
     </row>
@@ -2943,14 +2888,14 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Pay_AD</t>
+          <t>Pay_Overhaul</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>-12</v>
+        <v>-14</v>
       </c>
       <c r="E45" t="n">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -2959,7 +2904,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>advertising_expense | {"advertising_key": "本地:P1", "opportunities": 2}</t>
+          <t>management_fee_expense</t>
         </is>
       </c>
     </row>
@@ -2976,11 +2921,11 @@
         <v>-14</v>
       </c>
       <c r="E46" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>第5年1季</t>
+          <t>第5年2季</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -3002,11 +2947,11 @@
         <v>-14</v>
       </c>
       <c r="E47" t="n">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年3季</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3021,23 +2966,23 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Update_Receivable</t>
+          <t>Pay_Maintenance</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>81</v>
+        <v>-15</v>
       </c>
       <c r="E48" t="n">
-        <v>271</v>
+        <v>183</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>第5年2季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>receivable_collected | {"receivable_id": "AR-e4a8d018e2"}</t>
+          <t>maintenance_expense | {"line_id": "L-02a70490e9"}</t>
         </is>
       </c>
     </row>
@@ -3047,23 +2992,23 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Pay_Overhaul</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>-14</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>257</v>
+        <v>183</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>第5年3季</t>
+          <t>第5年4季</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>management_fee_expense</t>
+          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-02a70490e9", "asset_type": "factory"}</t>
         </is>
       </c>
     </row>
@@ -3073,14 +3018,14 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Pay_Maintenance</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>-15</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>242</v>
+        <v>183</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -3088,58 +3033,6 @@
         </is>
       </c>
       <c r="G50" t="inlineStr">
-        <is>
-          <t>maintenance_expense | {"line_id": "L-02a70490e9"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="B51" t="n">
-        <v>48</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" t="n">
-        <v>242</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>depreciation | {"amount_wan": 7.2, "asset_id": "F-02a70490e9", "asset_type": "factory"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="B52" t="n">
-        <v>49</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" t="n">
-        <v>242</v>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>第5年4季</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
         <is>
           <t>depreciation | {"amount_wan": 8.0, "asset_id": "L-02a70490e9", "asset_type": "production_line"}</t>
         </is>
@@ -3246,16 +3139,16 @@
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="H4" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -3471,16 +3364,16 @@
         <v>71</v>
       </c>
       <c r="E13" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F13" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G13" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H13" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15">
@@ -3536,13 +3429,13 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -3561,13 +3454,13 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -3586,13 +3479,13 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>67</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>41</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -3608,16 +3501,16 @@
         <v>71</v>
       </c>
       <c r="E19" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="F19" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="G19" t="n">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="H19" t="n">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20">
@@ -3633,16 +3526,16 @@
         <v>-71</v>
       </c>
       <c r="E20" t="n">
-        <v>-83</v>
+        <v>-79</v>
       </c>
       <c r="F20" t="n">
-        <v>-16</v>
+        <v>-66</v>
       </c>
       <c r="G20" t="n">
-        <v>-83</v>
+        <v>-79</v>
       </c>
       <c r="H20" t="n">
-        <v>-28</v>
+        <v>-65</v>
       </c>
     </row>
     <row r="21">
@@ -3683,16 +3576,16 @@
         <v>-86.2</v>
       </c>
       <c r="E22" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F22" t="n">
-        <v>-31.2</v>
+        <v>-81.2</v>
       </c>
       <c r="G22" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="H22" t="n">
-        <v>-43.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="23">
@@ -3733,16 +3626,16 @@
         <v>-86.2</v>
       </c>
       <c r="E24" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F24" t="n">
-        <v>-31.2</v>
+        <v>-81.2</v>
       </c>
       <c r="G24" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="H24" t="n">
-        <v>-43.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="25">
@@ -3783,16 +3676,16 @@
         <v>-86.2</v>
       </c>
       <c r="E26" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F26" t="n">
-        <v>-31.2</v>
+        <v>-81.2</v>
       </c>
       <c r="G26" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="H26" t="n">
-        <v>-43.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="28">
@@ -3882,16 +3775,16 @@
         <v>492</v>
       </c>
       <c r="E30" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F30" t="n">
-        <v>166</v>
+        <v>294</v>
       </c>
       <c r="G30" t="n">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="H30" t="n">
-        <v>242</v>
+        <v>183</v>
       </c>
     </row>
     <row r="31">
@@ -3910,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>147</v>
+        <v>33</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -3935,7 +3828,7 @@
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -3960,13 +3853,13 @@
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="G33" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="H33" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
     <row r="34">
@@ -4007,16 +3900,16 @@
         <v>492</v>
       </c>
       <c r="E35" t="n">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="F35" t="n">
-        <v>393</v>
+        <v>347</v>
       </c>
       <c r="G35" t="n">
-        <v>310</v>
+        <v>268</v>
       </c>
       <c r="H35" t="n">
-        <v>282</v>
+        <v>203</v>
       </c>
     </row>
     <row r="36">
@@ -4132,16 +4025,16 @@
         <v>588.8</v>
       </c>
       <c r="E40" t="n">
-        <v>490.6</v>
+        <v>494.6</v>
       </c>
       <c r="F40" t="n">
-        <v>459.4</v>
+        <v>413.4</v>
       </c>
       <c r="G40" t="n">
-        <v>361.2</v>
+        <v>319.2</v>
       </c>
       <c r="H40" t="n">
-        <v>318</v>
+        <v>239</v>
       </c>
     </row>
     <row r="41">
@@ -4310,13 +4203,13 @@
         <v>-86.20000000000003</v>
       </c>
       <c r="F47" t="n">
-        <v>-184.4000000000001</v>
+        <v>-180.4</v>
       </c>
       <c r="G47" t="n">
-        <v>-215.6000000000001</v>
+        <v>-261.6</v>
       </c>
       <c r="H47" t="n">
-        <v>-313.8000000000001</v>
+        <v>-355.8</v>
       </c>
     </row>
     <row r="48">
@@ -4332,16 +4225,16 @@
         <v>-86.2</v>
       </c>
       <c r="E48" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="F48" t="n">
-        <v>-31.2</v>
+        <v>-81.2</v>
       </c>
       <c r="G48" t="n">
-        <v>-98.2</v>
+        <v>-94.2</v>
       </c>
       <c r="H48" t="n">
-        <v>-43.2</v>
+        <v>-80.2</v>
       </c>
     </row>
     <row r="49">
@@ -4357,16 +4250,16 @@
         <v>588.8</v>
       </c>
       <c r="E49" t="n">
-        <v>490.6</v>
+        <v>494.6</v>
       </c>
       <c r="F49" t="n">
-        <v>459.3999999999999</v>
+        <v>413.4</v>
       </c>
       <c r="G49" t="n">
-        <v>361.1999999999999</v>
+        <v>319.2</v>
       </c>
       <c r="H49" t="n">
-        <v>317.9999999999999</v>
+        <v>239</v>
       </c>
     </row>
     <row r="50">
@@ -4382,16 +4275,16 @@
         <v>588.8</v>
       </c>
       <c r="E50" t="n">
-        <v>490.6</v>
+        <v>494.6</v>
       </c>
       <c r="F50" t="n">
-        <v>459.3999999999999</v>
+        <v>413.4</v>
       </c>
       <c r="G50" t="n">
-        <v>361.1999999999999</v>
+        <v>319.2</v>
       </c>
       <c r="H50" t="n">
-        <v>317.9999999999999</v>
+        <v>239</v>
       </c>
     </row>
   </sheetData>
@@ -4462,7 +4355,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
@@ -4611,7 +4504,7 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D12" t="n">
         <v>0</v>
@@ -4760,7 +4653,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D20" t="n">
         <v>0</v>
@@ -4909,7 +4802,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D28" t="n">
         <v>0</v>
@@ -5058,7 +4951,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>48</v>
+        <v>32</v>
       </c>
       <c r="D36" t="n">
         <v>0</v>
